--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="409">
   <si>
     <t/>
   </si>
@@ -76,321 +76,327 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
+    <t>10037376</t>
+  </si>
+  <si>
+    <t>NATUR-E VIT ALMH 16</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20073420</t>
+  </si>
+  <si>
+    <t>NATUR-E 300 DN 16'S</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20061582</t>
+  </si>
+  <si>
+    <t>MADU TJ JYBEE JRK100</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20135256</t>
+  </si>
+  <si>
+    <t>CURCUMA GROW ORGE100</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20137504</t>
+  </si>
+  <si>
+    <t>SKTNK/ABC C.MADU 24S</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10006069</t>
+  </si>
+  <si>
+    <t>SAKATONIK STR 30X800</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>10016755</t>
+  </si>
+  <si>
+    <t>GELIGA BALSAM OTOT20</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>10000549</t>
+  </si>
+  <si>
+    <t>COUNTERPAIN CREAM 30</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20047965</t>
+  </si>
+  <si>
+    <t>HOT IN CREAM 120ML</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20057841</t>
+  </si>
+  <si>
+    <t>HOT IN CREAM 60G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20080244</t>
+  </si>
+  <si>
+    <t>HOT IN CRM STRNG 120</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20019446</t>
+  </si>
+  <si>
+    <t>C/LANG MINYAK GPU 60</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20054951</t>
+  </si>
+  <si>
+    <t>S/M TOLAK/A ANAK 5'S</t>
+  </si>
+  <si>
+    <t>20034577</t>
+  </si>
+  <si>
+    <t>S/M TLK.ANGN+MDU 5'S</t>
+  </si>
+  <si>
+    <t>20122907</t>
+  </si>
+  <si>
+    <t>S/M TLK.ANGN FLU 5'S</t>
+  </si>
+  <si>
+    <t>20064502</t>
+  </si>
+  <si>
+    <t>S/M TLK ANGIN BG 5'S</t>
+  </si>
+  <si>
+    <t>20064503</t>
+  </si>
+  <si>
+    <t>S/M TLK LINU HRB 5'S</t>
+  </si>
+  <si>
+    <t>20059240</t>
+  </si>
+  <si>
+    <t>ANTANGIN JUNIOR 5'S</t>
+  </si>
+  <si>
+    <t>20041621</t>
+  </si>
+  <si>
+    <t>ANTANGIN JRG 5X15ML</t>
+  </si>
+  <si>
+    <t>20114432</t>
+  </si>
+  <si>
+    <t>ANTANGIN HTBTSDA 5'S</t>
+  </si>
+  <si>
+    <t>20054969</t>
+  </si>
+  <si>
+    <t>ANTANGIN GNGR/M 5X15</t>
+  </si>
+  <si>
+    <t>20093959</t>
+  </si>
+  <si>
+    <t>BEJO JAHE MERAH 6X15</t>
+  </si>
+  <si>
+    <t>20137415</t>
+  </si>
+  <si>
+    <t>MXGRP GRGES JLM 6S</t>
+  </si>
+  <si>
+    <t>20124231</t>
+  </si>
+  <si>
+    <t>MADU TJ MSK ANGIN140</t>
+  </si>
+  <si>
+    <t>20088783</t>
+  </si>
+  <si>
+    <t>MADU TJ PNS DLM 150</t>
+  </si>
+  <si>
     <t>10003799</t>
   </si>
   <si>
     <t>EXTRA JOSS BOX 6'S</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>20139960</t>
   </si>
   <si>
     <t>EJ SPORT ORANGE 2S</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10037376</t>
-  </si>
-  <si>
-    <t>NATUR-E VIT ALMH 16</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20073420</t>
-  </si>
-  <si>
-    <t>NATUR-E 300 DN 16'S</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20061582</t>
-  </si>
-  <si>
-    <t>MADU TJ JYBEE JRK100</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>RT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20135256</t>
-  </si>
-  <si>
-    <t>CURCUMA GROW ORGE100</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20137504</t>
-  </si>
-  <si>
-    <t>SKTNK/ABC C.MADU 24S</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>10006069</t>
-  </si>
-  <si>
-    <t>SAKATONIK STR 30X800</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10000549</t>
-  </si>
-  <si>
-    <t>COUNTERPAIN CREAM 30</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20047965</t>
-  </si>
-  <si>
-    <t>HOT IN CREAM 120ML</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20057841</t>
-  </si>
-  <si>
-    <t>HOT IN CREAM 60G</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20080244</t>
-  </si>
-  <si>
-    <t>HOT IN CRM STRNG 120</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20019446</t>
-  </si>
-  <si>
-    <t>C/LANG MINYAK GPU 60</t>
+    <t>10030787</t>
+  </si>
+  <si>
+    <t>ACTF PILEK&amp;BT.DHK 60</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138372</t>
+  </si>
+  <si>
+    <t>KOMIX OBH 6X7ML</t>
+  </si>
+  <si>
+    <t>20092712</t>
+  </si>
+  <si>
+    <t>KOMIX HERBAL 4X15ML</t>
+  </si>
+  <si>
+    <t>10008599</t>
+  </si>
+  <si>
+    <t>OBH/C ANAK STRW 60ML</t>
+  </si>
+  <si>
+    <t>10023206</t>
+  </si>
+  <si>
+    <t>TERMOREX PLUS 60 ML</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10006565</t>
+  </si>
+  <si>
+    <t>TEMPRA T/PNS ANGR 60</t>
+  </si>
+  <si>
+    <t>10000548</t>
+  </si>
+  <si>
+    <t>CAP LANG NORIT (40)</t>
+  </si>
+  <si>
+    <t>10038823</t>
+  </si>
+  <si>
+    <t>COMBANTRIN JRK 10ML</t>
+  </si>
+  <si>
+    <t>20021454</t>
+  </si>
+  <si>
+    <t>MYLANTA MAAG MINT 50</t>
+  </si>
+  <si>
+    <t>20052643</t>
+  </si>
+  <si>
+    <t>PROMAG HRBAL BOX 6'S</t>
+  </si>
+  <si>
+    <t>20057840</t>
+  </si>
+  <si>
+    <t>POLYSILANE BTL 100</t>
+  </si>
+  <si>
+    <t>20021214</t>
+  </si>
+  <si>
+    <t>VGTA HERBAL ANGR 6'S</t>
+  </si>
+  <si>
+    <t>20107145</t>
+  </si>
+  <si>
+    <t>DULCOLAX 10'S</t>
+  </si>
+  <si>
+    <t>20002523</t>
+  </si>
+  <si>
+    <t>ROHTO OBT MATA COL 7</t>
+  </si>
+  <si>
+    <t>20105059</t>
+  </si>
+  <si>
+    <t>ROHTO V-EXTRA 7ML</t>
+  </si>
+  <si>
+    <t>10000149</t>
+  </si>
+  <si>
+    <t>INSTO REG. 7.5 ML</t>
+  </si>
+  <si>
+    <t>10015684</t>
+  </si>
+  <si>
+    <t>INSTO FRY EYES 7.5</t>
+  </si>
+  <si>
+    <t>20122751</t>
+  </si>
+  <si>
+    <t>INSTO COOL 7.5ML</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20054951</t>
-  </si>
-  <si>
-    <t>S/M TOLAK/A ANAK 5'S</t>
-  </si>
-  <si>
-    <t>20034577</t>
-  </si>
-  <si>
-    <t>S/M TLK.ANGN+MDU 5'S</t>
-  </si>
-  <si>
-    <t>20122907</t>
-  </si>
-  <si>
-    <t>S/M TLK.ANGN FLU 5'S</t>
-  </si>
-  <si>
-    <t>20064502</t>
-  </si>
-  <si>
-    <t>S/M TLK ANGIN BG 5'S</t>
-  </si>
-  <si>
-    <t>20064503</t>
-  </si>
-  <si>
-    <t>S/M TLK LINU HRB 5'S</t>
-  </si>
-  <si>
-    <t>20059240</t>
-  </si>
-  <si>
-    <t>ANTANGIN JUNIOR 5'S</t>
-  </si>
-  <si>
-    <t>20041621</t>
-  </si>
-  <si>
-    <t>ANTANGIN JRG 5X15ML</t>
-  </si>
-  <si>
-    <t>20114432</t>
-  </si>
-  <si>
-    <t>ANTANGIN HTBTSDA 5'S</t>
-  </si>
-  <si>
-    <t>20054969</t>
-  </si>
-  <si>
-    <t>ANTANGIN GNGR/M 5X15</t>
-  </si>
-  <si>
-    <t>20093959</t>
-  </si>
-  <si>
-    <t>BEJO JAHE MERAH 6X15</t>
-  </si>
-  <si>
-    <t>20137415</t>
-  </si>
-  <si>
-    <t>MXGRP GRGES JLM 6S</t>
-  </si>
-  <si>
-    <t>20124231</t>
-  </si>
-  <si>
-    <t>MADU TJ MSK ANGIN140</t>
-  </si>
-  <si>
-    <t>20088783</t>
-  </si>
-  <si>
-    <t>MADU TJ PNS DLM 150</t>
-  </si>
-  <si>
-    <t>10030787</t>
-  </si>
-  <si>
-    <t>ACTF PILEK&amp;BT.DHK 60</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138372</t>
-  </si>
-  <si>
-    <t>KOMIX OBH 6X7ML</t>
-  </si>
-  <si>
-    <t>20092712</t>
-  </si>
-  <si>
-    <t>KOMIX HERBAL 4X15ML</t>
-  </si>
-  <si>
-    <t>10008599</t>
-  </si>
-  <si>
-    <t>OBH/C ANAK STRW 60ML</t>
-  </si>
-  <si>
-    <t>10023206</t>
-  </si>
-  <si>
-    <t>TERMOREX PLUS 60 ML</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10006565</t>
-  </si>
-  <si>
-    <t>TEMPRA T/PNS ANGR 60</t>
-  </si>
-  <si>
-    <t>10000548</t>
-  </si>
-  <si>
-    <t>CAP LANG NORIT (40)</t>
-  </si>
-  <si>
-    <t>10038823</t>
-  </si>
-  <si>
-    <t>COMBANTRIN JRK 10ML</t>
-  </si>
-  <si>
-    <t>20021454</t>
-  </si>
-  <si>
-    <t>MYLANTA MAAG MINT 50</t>
-  </si>
-  <si>
-    <t>20052643</t>
-  </si>
-  <si>
-    <t>PROMAG HRBAL BOX 6'S</t>
-  </si>
-  <si>
-    <t>20057840</t>
-  </si>
-  <si>
-    <t>POLYSILANE BTL 100</t>
-  </si>
-  <si>
-    <t>20021214</t>
-  </si>
-  <si>
-    <t>VGTA HERBAL ANGR 6'S</t>
-  </si>
-  <si>
-    <t>20107145</t>
-  </si>
-  <si>
-    <t>DULCOLAX 10'S</t>
-  </si>
-  <si>
-    <t>20002523</t>
-  </si>
-  <si>
-    <t>ROHTO OBT MATA COL 7</t>
-  </si>
-  <si>
-    <t>20105059</t>
-  </si>
-  <si>
-    <t>ROHTO V-EXTRA 7ML</t>
-  </si>
-  <si>
-    <t>10000149</t>
-  </si>
-  <si>
-    <t>INSTO REG. 7.5 ML</t>
-  </si>
-  <si>
-    <t>10015684</t>
-  </si>
-  <si>
-    <t>INSTO FRY EYES 7.5</t>
-  </si>
-  <si>
-    <t>20122751</t>
-  </si>
-  <si>
-    <t>INSTO COOL 7.5ML</t>
-  </si>
-  <si>
     <t>20129405</t>
   </si>
   <si>
@@ -625,42 +631,33 @@
     <t>20</t>
   </si>
   <si>
-    <t>10016755</t>
-  </si>
-  <si>
-    <t>GELIGA BALSAM OTOT20</t>
+    <t>10000553</t>
+  </si>
+  <si>
+    <t>BETADINE SOLUTION 30</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>10000553</t>
-  </si>
-  <si>
-    <t>BETADINE SOLUTION 30</t>
+    <t>20137313</t>
+  </si>
+  <si>
+    <t>HANSPLST ANTSP 40ML</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>20137313</t>
-  </si>
-  <si>
-    <t>HANSPLST ANTSP 40ML</t>
+    <t>10002676</t>
+  </si>
+  <si>
+    <t>IKA ALKOHOL 70%100ML</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>10002676</t>
-  </si>
-  <si>
-    <t>IKA ALKOHOL 70%100ML</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>10000473</t>
   </si>
   <si>
@@ -727,6 +724,12 @@
     <t>PANADOL FLU&amp;BTK 10'S</t>
   </si>
   <si>
+    <t>10000098</t>
+  </si>
+  <si>
+    <t>CABE KOYO KECIL (10)</t>
+  </si>
+  <si>
     <t>10004359</t>
   </si>
   <si>
@@ -751,22 +754,58 @@
     <t>SALONPAS EX.HOT 5X2S</t>
   </si>
   <si>
+    <t>10000073</t>
+  </si>
+  <si>
+    <t>PARAMEX SKT KEPALA 4</t>
+  </si>
+  <si>
+    <t>20129404</t>
+  </si>
+  <si>
+    <t>BYE BYE-FEVER DEWASA</t>
+  </si>
+  <si>
+    <t>20136473</t>
+  </si>
+  <si>
+    <t>ANTIMO ANAK JERUK5'S</t>
+  </si>
+  <si>
     <t>20138270</t>
   </si>
   <si>
     <t>DETTOL ANTSP PLST 10</t>
   </si>
   <si>
-    <t>10000073</t>
-  </si>
-  <si>
-    <t>PARAMEX SKT KEPALA 4</t>
-  </si>
-  <si>
-    <t>10000098</t>
-  </si>
-  <si>
-    <t>CABE KOYO KECIL (10)</t>
+    <t>20141639</t>
+  </si>
+  <si>
+    <t>SKTONIK ACTV GUMMY6S</t>
+  </si>
+  <si>
+    <t>10000155</t>
+  </si>
+  <si>
+    <t>DECOLGEN TABLET(4'S)</t>
+  </si>
+  <si>
+    <t>10000555</t>
+  </si>
+  <si>
+    <t>ANTIMO 10'S</t>
+  </si>
+  <si>
+    <t>10000621</t>
+  </si>
+  <si>
+    <t>SANGOBION (10'S)</t>
+  </si>
+  <si>
+    <t>20044054</t>
+  </si>
+  <si>
+    <t>C/LANG KOOLFEVER BYI</t>
   </si>
   <si>
     <t>20065430</t>
@@ -775,28 +814,10 @@
     <t>HNSAPLAST AQUA PRO 6</t>
   </si>
   <si>
-    <t>20129404</t>
-  </si>
-  <si>
-    <t>BYE BYE-FEVER DEWASA</t>
-  </si>
-  <si>
-    <t>20136473</t>
-  </si>
-  <si>
-    <t>ANTIMO ANAK JERUK5'S</t>
-  </si>
-  <si>
-    <t>10000155</t>
-  </si>
-  <si>
-    <t>DECOLGEN TABLET(4'S)</t>
-  </si>
-  <si>
-    <t>10000555</t>
-  </si>
-  <si>
-    <t>ANTIMO 10'S</t>
+    <t>10000154</t>
+  </si>
+  <si>
+    <t>NEOZEP FORTE STR.4'S</t>
   </si>
   <si>
     <t>10003514</t>
@@ -805,10 +826,133 @@
     <t>H/PLAST KAIN ELAST10</t>
   </si>
   <si>
-    <t>20044054</t>
-  </si>
-  <si>
-    <t>C/LANG KOOLFEVER BYI</t>
+    <t>10028800</t>
+  </si>
+  <si>
+    <t>NEO RHMCYL NEURO 10S</t>
+  </si>
+  <si>
+    <t>20029331</t>
+  </si>
+  <si>
+    <t>C/LANG KOOLFEVER ANK</t>
+  </si>
+  <si>
+    <t>20112905</t>
+  </si>
+  <si>
+    <t>FATIGON SPIRIT 6'S</t>
+  </si>
+  <si>
+    <t>10000452</t>
+  </si>
+  <si>
+    <t>ULTRA FLU 4'S</t>
+  </si>
+  <si>
+    <t>10035326</t>
+  </si>
+  <si>
+    <t>HEMAVITON STAMINA5'S</t>
+  </si>
+  <si>
+    <t>20113365</t>
+  </si>
+  <si>
+    <t>PROMAG 10'S</t>
+  </si>
+  <si>
+    <t>20122436</t>
+  </si>
+  <si>
+    <t>CL KOOL FEVER DEWASA</t>
+  </si>
+  <si>
+    <t>20133187</t>
+  </si>
+  <si>
+    <t>H/PLAST KAIN FUN10'S</t>
+  </si>
+  <si>
+    <t>10000075</t>
+  </si>
+  <si>
+    <t>KONIDIN OBAT BTK 4'S</t>
+  </si>
+  <si>
+    <t>10000665</t>
+  </si>
+  <si>
+    <t>MYLANTA OBAT MAAG 10</t>
+  </si>
+  <si>
+    <t>10003995</t>
+  </si>
+  <si>
+    <t>HEMAVITON ACTION 5'S</t>
+  </si>
+  <si>
+    <t>20137316</t>
+  </si>
+  <si>
+    <t>HNSPLST  TRANSP 10'S</t>
+  </si>
+  <si>
+    <t>20137414</t>
+  </si>
+  <si>
+    <t>DOLO NEUROBION 10S</t>
+  </si>
+  <si>
+    <t>TG,(E-4B)</t>
+  </si>
+  <si>
+    <t>10010246</t>
+  </si>
+  <si>
+    <t>NEUROBION VIT.10'S</t>
+  </si>
+  <si>
+    <t>10030867</t>
+  </si>
+  <si>
+    <t>PROCOLD OBAT FLU 6'S</t>
+  </si>
+  <si>
+    <t>20027551</t>
+  </si>
+  <si>
+    <t>HOLSTICARE ESTR C 4S</t>
+  </si>
+  <si>
+    <t>20120361</t>
+  </si>
+  <si>
+    <t>ENTROSTOP STR 10'S</t>
+  </si>
+  <si>
+    <t>20120928</t>
+  </si>
+  <si>
+    <t>IM-BOOST VIT C&amp;D3 4S</t>
+  </si>
+  <si>
+    <t>20010358</t>
+  </si>
+  <si>
+    <t>MXAGRIP FLU&amp;BATUK 4S</t>
+  </si>
+  <si>
+    <t>20053803</t>
+  </si>
+  <si>
+    <t>NEUROBION FORTE 10'S</t>
+  </si>
+  <si>
+    <t>20056311</t>
+  </si>
+  <si>
+    <t>CEREBRF.GUMMY STR20G</t>
   </si>
   <si>
     <t>20087096</t>
@@ -817,175 +961,46 @@
     <t>IM-BOOST TABLET 4'S</t>
   </si>
   <si>
-    <t>10000154</t>
-  </si>
-  <si>
-    <t>NEOZEP FORTE STR.4'S</t>
-  </si>
-  <si>
-    <t>10028800</t>
-  </si>
-  <si>
-    <t>NEO RHMCYL NEURO 10S</t>
-  </si>
-  <si>
-    <t>20029331</t>
-  </si>
-  <si>
-    <t>C/LANG KOOLFEVER ANK</t>
-  </si>
-  <si>
-    <t>20120928</t>
-  </si>
-  <si>
-    <t>IM-BOOST VIT C&amp;D3 4S</t>
-  </si>
-  <si>
-    <t>20133187</t>
-  </si>
-  <si>
-    <t>H/PLAST KAIN FUN10'S</t>
-  </si>
-  <si>
-    <t>10000452</t>
-  </si>
-  <si>
-    <t>ULTRA FLU 4'S</t>
-  </si>
-  <si>
-    <t>20098028</t>
-  </si>
-  <si>
-    <t>SAKATONIK ACTIV 6'S</t>
-  </si>
-  <si>
-    <t>20113365</t>
-  </si>
-  <si>
-    <t>PROMAG 10'S</t>
-  </si>
-  <si>
-    <t>20122436</t>
-  </si>
-  <si>
-    <t>CL KOOL FEVER DEWASA</t>
-  </si>
-  <si>
-    <t>20137316</t>
-  </si>
-  <si>
-    <t>HNSPLST  TRANSP 10'S</t>
-  </si>
-  <si>
-    <t>10000075</t>
-  </si>
-  <si>
-    <t>KONIDIN OBAT BTK 4'S</t>
-  </si>
-  <si>
-    <t>10000621</t>
-  </si>
-  <si>
-    <t>SANGOBION (10'S)</t>
-  </si>
-  <si>
-    <t>10000665</t>
-  </si>
-  <si>
-    <t>MYLANTA OBAT MAAG 10</t>
-  </si>
-  <si>
-    <t>10010246</t>
-  </si>
-  <si>
-    <t>NEUROBION VIT.10'S</t>
-  </si>
-  <si>
-    <t>10035326</t>
-  </si>
-  <si>
-    <t>HEMAVITON STAMINA5'S</t>
-  </si>
-  <si>
-    <t>10003995</t>
-  </si>
-  <si>
-    <t>HEMAVITON ACTION 5'S</t>
-  </si>
-  <si>
-    <t>10030867</t>
-  </si>
-  <si>
-    <t>PROCOLD OBAT FLU 6'S</t>
-  </si>
-  <si>
-    <t>20053803</t>
-  </si>
-  <si>
-    <t>NEUROBION FORTE 10'S</t>
-  </si>
-  <si>
-    <t>20120361</t>
-  </si>
-  <si>
-    <t>ENTROSTOP STR 10'S</t>
-  </si>
-  <si>
-    <t>20137414</t>
-  </si>
-  <si>
-    <t>DOLO NEUROBION 10S</t>
-  </si>
-  <si>
-    <t>TG,(E-4B)</t>
-  </si>
-  <si>
-    <t>20010358</t>
-  </si>
-  <si>
-    <t>MXAGRIP FLU&amp;BATUK 4S</t>
-  </si>
-  <si>
-    <t>20056311</t>
-  </si>
-  <si>
-    <t>CEREBRF.GUMMY STR20G</t>
-  </si>
-  <si>
     <t>20090384</t>
   </si>
   <si>
     <t>DIAPET KAPSUL 10'S</t>
   </si>
   <si>
+    <t>10000069</t>
+  </si>
+  <si>
+    <t>MIXAGRIP O.SKT FLU4S</t>
+  </si>
+  <si>
+    <t>10003650</t>
+  </si>
+  <si>
+    <t>ENERVON C TABLET 4'S</t>
+  </si>
+  <si>
+    <t>20090383</t>
+  </si>
+  <si>
+    <t>LAXING STR 10'S</t>
+  </si>
+  <si>
     <t>20102471</t>
   </si>
   <si>
     <t>CDR VITAMIN C 2'S</t>
   </si>
   <si>
-    <t>20112905</t>
-  </si>
-  <si>
-    <t>FATIGON SPIRIT 6'S</t>
-  </si>
-  <si>
-    <t>10000069</t>
-  </si>
-  <si>
-    <t>MIXAGRIP O.SKT FLU4S</t>
-  </si>
-  <si>
-    <t>20027551</t>
-  </si>
-  <si>
-    <t>HOLSTICARE ESTR C 4S</t>
-  </si>
-  <si>
-    <t>20090383</t>
-  </si>
-  <si>
-    <t>LAXING STR 10'S</t>
+    <t>20014241</t>
+  </si>
+  <si>
+    <t>AMBEVEN U/ WASR 10'S</t>
+  </si>
+  <si>
+    <t>20057705</t>
+  </si>
+  <si>
+    <t>KONIDIN OBAT BTK 5X7</t>
   </si>
   <si>
     <t>20124298</t>
@@ -994,22 +1009,10 @@
     <t>IM-BOOST BONE ORG 2S</t>
   </si>
   <si>
-    <t>10003650</t>
-  </si>
-  <si>
-    <t>ENERVON C TABLET 4'S</t>
-  </si>
-  <si>
-    <t>20014241</t>
-  </si>
-  <si>
-    <t>AMBEVEN U/ WASR 10'S</t>
-  </si>
-  <si>
-    <t>20057705</t>
-  </si>
-  <si>
-    <t>KONIDIN OBAT BTK 5X7</t>
+    <t>20048747</t>
+  </si>
+  <si>
+    <t>MICROLAX GEL 5ML</t>
   </si>
   <si>
     <t>20083486</t>
@@ -1018,34 +1021,28 @@
     <t>REDOXON JERUK 2'S</t>
   </si>
   <si>
-    <t>20048747</t>
-  </si>
-  <si>
-    <t>MICROLAX GEL 5ML</t>
+    <t>20140912</t>
+  </si>
+  <si>
+    <t>SM TOLAK ANGIN 15ML</t>
+  </si>
+  <si>
+    <t>10000197</t>
+  </si>
+  <si>
+    <t>VITACIMIN STRIP 2'S</t>
+  </si>
+  <si>
+    <t>20124837</t>
+  </si>
+  <si>
+    <t>KALPANAX SALEP 6G</t>
   </si>
   <si>
     <t>20132440</t>
   </si>
   <si>
     <t>ULTRA CAP GOLD VIT4S</t>
-  </si>
-  <si>
-    <t>20140912</t>
-  </si>
-  <si>
-    <t>SM TOLAK ANGIN 15ML</t>
-  </si>
-  <si>
-    <t>10000197</t>
-  </si>
-  <si>
-    <t>VITACIMIN STRIP 2'S</t>
-  </si>
-  <si>
-    <t>20124837</t>
-  </si>
-  <si>
-    <t>KALPANAX SALEP 6G</t>
   </si>
   <si>
     <t>10003980</t>
@@ -1801,7 +1798,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1821,15 +1818,15 @@
         <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1838,18 +1835,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1858,10 +1855,10 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1881,7 +1878,7 @@
         <v>39</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1901,15 +1898,15 @@
         <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1918,18 +1915,18 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1938,18 +1935,18 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1958,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1966,10 +1963,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1978,7 +1975,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1986,10 +1983,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1998,38 +1995,38 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2038,7 +2035,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>12</v>
@@ -2046,10 +2043,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2058,7 +2055,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -2066,10 +2063,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -2078,7 +2075,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>12</v>
@@ -2086,10 +2083,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -2098,7 +2095,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>12</v>
@@ -2106,10 +2103,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -2118,18 +2115,18 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -2138,7 +2135,7 @@
         <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2146,10 +2143,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -2158,7 +2155,7 @@
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2166,10 +2163,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -2178,7 +2175,7 @@
         <v>8</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2186,10 +2183,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2198,18 +2195,18 @@
         <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -2218,7 +2215,7 @@
         <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>20</v>
@@ -2226,10 +2223,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2238,18 +2235,18 @@
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2258,18 +2255,18 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -2278,38 +2275,38 @@
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -2318,18 +2315,18 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2338,7 +2335,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>20</v>
@@ -2346,10 +2343,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2358,7 +2355,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>20</v>
@@ -2366,10 +2363,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2378,18 +2375,18 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2398,18 +2395,18 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2418,18 +2415,18 @@
         <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2438,18 +2435,18 @@
         <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2458,7 +2455,7 @@
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>20</v>
@@ -2466,10 +2463,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2478,18 +2475,18 @@
         <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2498,18 +2495,18 @@
         <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2518,18 +2515,18 @@
         <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2538,18 +2535,18 @@
         <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2558,7 +2555,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>20</v>
@@ -2566,10 +2563,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2578,7 +2575,7 @@
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>20</v>
@@ -2586,10 +2583,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2598,7 +2595,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>20</v>
@@ -2606,10 +2603,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2618,7 +2615,7 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>20</v>
@@ -2626,10 +2623,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2638,7 +2635,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>20</v>
@@ -2646,30 +2643,30 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2678,18 +2675,18 @@
         <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2698,10 +2695,10 @@
         <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2718,10 +2715,10 @@
         <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2738,10 +2735,10 @@
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2758,10 +2755,10 @@
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2778,10 +2775,10 @@
         <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2798,10 +2795,10 @@
         <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2818,10 +2815,10 @@
         <v>15</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2838,10 +2835,10 @@
         <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2858,7 +2855,7 @@
         <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2878,10 +2875,10 @@
         <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2898,10 +2895,10 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2918,10 +2915,10 @@
         <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2938,10 +2935,10 @@
         <v>15</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2958,10 +2955,10 @@
         <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2978,10 +2975,10 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2995,13 +2992,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3018,7 +3015,7 @@
         <v>19</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3038,7 +3035,7 @@
         <v>19</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3058,7 +3055,7 @@
         <v>19</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3078,7 +3075,7 @@
         <v>19</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3098,7 +3095,7 @@
         <v>19</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3118,7 +3115,7 @@
         <v>19</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3138,7 +3135,7 @@
         <v>19</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3158,7 +3155,7 @@
         <v>19</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3178,7 +3175,7 @@
         <v>19</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3198,7 +3195,7 @@
         <v>19</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3218,7 +3215,7 @@
         <v>19</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3238,10 +3235,10 @@
         <v>19</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,10 +3255,10 @@
         <v>19</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3278,10 +3275,10 @@
         <v>19</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,10 +3295,10 @@
         <v>19</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3318,7 +3315,7 @@
         <v>19</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>20</v>
@@ -3338,7 +3335,7 @@
         <v>19</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>20</v>
@@ -3358,18 +3355,18 @@
         <v>19</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>200</v>
+        <v>127</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3378,18 +3375,18 @@
         <v>19</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3398,18 +3395,18 @@
         <v>19</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3418,18 +3415,18 @@
         <v>19</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3438,7 +3435,7 @@
         <v>19</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>20</v>
@@ -3446,10 +3443,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3458,18 +3455,18 @@
         <v>19</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3486,10 +3483,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3501,15 +3498,15 @@
         <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3526,10 +3523,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3541,15 +3538,15 @@
         <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3561,15 +3558,15 @@
         <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3581,15 +3578,15 @@
         <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3601,15 +3598,15 @@
         <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3621,15 +3618,15 @@
         <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3641,15 +3638,15 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3661,15 +3658,15 @@
         <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3681,15 +3678,15 @@
         <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3701,15 +3698,15 @@
         <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3721,15 +3718,15 @@
         <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>20</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3741,15 +3738,15 @@
         <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>224</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3761,15 +3758,15 @@
         <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>20</v>
+        <v>223</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3781,15 +3778,15 @@
         <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3801,15 +3798,15 @@
         <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3821,15 +3818,15 @@
         <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3841,15 +3838,15 @@
         <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3866,10 +3863,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3886,10 +3883,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3906,10 +3903,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3921,15 +3918,15 @@
         <v>19</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3946,10 +3943,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3961,15 +3958,15 @@
         <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3986,11 +3983,11 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
@@ -4001,16 +3998,16 @@
         <v>23</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>229</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
@@ -4021,16 +4018,16 @@
         <v>23</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>61</v>
+        <v>228</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
@@ -4041,16 +4038,16 @@
         <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
@@ -4061,15 +4058,15 @@
         <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4086,10 +4083,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4101,15 +4098,15 @@
         <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4126,10 +4123,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4146,10 +4143,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4161,15 +4158,15 @@
         <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4181,15 +4178,15 @@
         <v>29</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4201,15 +4198,15 @@
         <v>29</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>131</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4221,15 +4218,15 @@
         <v>29</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4241,15 +4238,15 @@
         <v>29</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>224</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4261,7 +4258,7 @@
         <v>29</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>229</v>
+        <v>297</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4278,10 +4275,10 @@
         <v>23</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4298,7 +4295,7 @@
         <v>23</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>12</v>
@@ -4318,10 +4315,10 @@
         <v>23</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>131</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4338,7 +4335,7 @@
         <v>23</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>20</v>
@@ -4358,19 +4355,19 @@
         <v>23</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>308</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
@@ -4378,7 +4375,7 @@
         <v>23</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>12</v>
@@ -4386,11 +4383,11 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
@@ -4398,19 +4395,19 @@
         <v>23</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
@@ -4418,19 +4415,19 @@
         <v>23</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
@@ -4438,19 +4435,19 @@
         <v>23</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
@@ -4458,18 +4455,18 @@
         <v>23</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -4486,10 +4483,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -4501,15 +4498,15 @@
         <v>39</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4526,10 +4523,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4546,10 +4543,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -4561,15 +4558,15 @@
         <v>42</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
@@ -4581,15 +4578,15 @@
         <v>42</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
@@ -4601,16 +4598,16 @@
         <v>42</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
@@ -4618,7 +4615,7 @@
         <v>23</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4626,11 +4623,11 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
@@ -4638,7 +4635,7 @@
         <v>23</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4646,11 +4643,11 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
@@ -4658,19 +4655,19 @@
         <v>23</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
@@ -4678,19 +4675,19 @@
         <v>23</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
@@ -4698,19 +4695,19 @@
         <v>23</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
@@ -4718,19 +4715,19 @@
         <v>23</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
@@ -4738,7 +4735,7 @@
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>20</v>
@@ -4746,31 +4743,31 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
@@ -4778,7 +4775,7 @@
         <v>23</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>12</v>
@@ -4786,11 +4783,11 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
@@ -4798,7 +4795,7 @@
         <v>23</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>12</v>
@@ -4806,11 +4803,11 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
@@ -4818,19 +4815,19 @@
         <v>23</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
@@ -4838,7 +4835,7 @@
         <v>23</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>12</v>
@@ -4846,10 +4843,10 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
@@ -4861,15 +4858,15 @@
         <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
@@ -4881,15 +4878,15 @@
         <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
@@ -4901,15 +4898,15 @@
         <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
@@ -4926,10 +4923,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
@@ -4941,15 +4938,15 @@
         <v>19</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
@@ -4961,15 +4958,15 @@
         <v>23</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
@@ -4981,15 +4978,15 @@
         <v>26</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
@@ -5001,15 +4998,15 @@
         <v>29</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
@@ -5018,18 +5015,18 @@
         <v>26</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
@@ -5038,7 +5035,7 @@
         <v>26</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>20</v>
@@ -5046,10 +5043,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
@@ -5066,10 +5063,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
@@ -5081,15 +5078,15 @@
         <v>42</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
@@ -5098,7 +5095,7 @@
         <v>26</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5106,10 +5103,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
@@ -5118,18 +5115,18 @@
         <v>26</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>387</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
@@ -5146,10 +5143,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -5166,10 +5163,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5186,10 +5183,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5206,10 +5203,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5226,10 +5223,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5246,10 +5243,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5266,10 +5263,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
@@ -5286,10 +5283,10 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
@@ -5298,7 +5295,7 @@
         <v>29</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>20</v>
@@ -5306,10 +5303,10 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
@@ -5318,7 +5315,7 @@
         <v>29</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>20</v>
@@ -5326,10 +5323,10 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
@@ -5341,15 +5338,15 @@
         <v>39</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
@@ -5361,7 +5358,7 @@
         <v>42</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
